--- a/artfynd/A 18322-2026 artfynd.xlsx
+++ b/artfynd/A 18322-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133804702</v>
+        <v>133804657</v>
       </c>
       <c r="B2" t="n">
-        <v>57153</v>
+        <v>91960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486313</v>
+        <v>486285</v>
       </c>
       <c r="R2" t="n">
-        <v>7044870</v>
+        <v>7044755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804657</v>
+        <v>133804702</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>57153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486285</v>
+        <v>486313</v>
       </c>
       <c r="R4" t="n">
-        <v>7044755</v>
+        <v>7044870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133804681</v>
+        <v>133804652</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486221</v>
+        <v>486530</v>
       </c>
       <c r="R5" t="n">
-        <v>7044782</v>
+        <v>7044741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1045,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133804666</v>
+        <v>133804651</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486263</v>
+        <v>486539</v>
       </c>
       <c r="R6" t="n">
-        <v>7044932</v>
+        <v>7044715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,11 +1142,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133804652</v>
+        <v>133804658</v>
       </c>
       <c r="B7" t="n">
-        <v>91960</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1213,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486530</v>
+        <v>486571</v>
       </c>
       <c r="R7" t="n">
-        <v>7044741</v>
+        <v>7044726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,32 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133804658</v>
+        <v>133804653</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>91960</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486571</v>
+        <v>486466</v>
       </c>
       <c r="R8" t="n">
-        <v>7044726</v>
+        <v>7044734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133804679</v>
+        <v>133804721</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>83208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486219</v>
+        <v>486382</v>
       </c>
       <c r="R9" t="n">
-        <v>7044793</v>
+        <v>7044675</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,11 +1433,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133804670</v>
+        <v>133804715</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1485,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1509,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486250</v>
+        <v>486526</v>
       </c>
       <c r="R10" t="n">
-        <v>7044887</v>
+        <v>7044708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,11 +1530,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133804651</v>
+        <v>133804713</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486539</v>
+        <v>486386</v>
       </c>
       <c r="R11" t="n">
-        <v>7044715</v>
+        <v>7044674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133804653</v>
+        <v>133804650</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>97421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486466</v>
+        <v>486266</v>
       </c>
       <c r="R12" t="n">
-        <v>7044734</v>
+        <v>7044804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133804665</v>
+        <v>133804707</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,54 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486305</v>
+        <v>486370</v>
       </c>
       <c r="R13" t="n">
-        <v>7044896</v>
+        <v>7044652</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,11 +1821,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 födosökande/ringhackande hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133804661</v>
+        <v>133804655</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486467</v>
+        <v>486471</v>
       </c>
       <c r="R14" t="n">
-        <v>7044758</v>
+        <v>7044756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,11 +1918,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133804676</v>
+        <v>133804710</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486230</v>
+        <v>486224</v>
       </c>
       <c r="R15" t="n">
-        <v>7044828</v>
+        <v>7044799</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,11 +2015,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133804721</v>
+        <v>133804700</v>
       </c>
       <c r="B16" t="n">
-        <v>83208</v>
+        <v>57153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,34 +2052,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486382</v>
+        <v>486493</v>
       </c>
       <c r="R16" t="n">
-        <v>7044675</v>
+        <v>7044752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804689</v>
+        <v>133804697</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>92392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2228,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486443</v>
+        <v>486485</v>
       </c>
       <c r="R17" t="n">
-        <v>7044686</v>
+        <v>7044754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2264,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,10 +2243,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804660</v>
+        <v>133804705</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2306,21 +2254,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2330,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486477</v>
+        <v>486296</v>
       </c>
       <c r="R18" t="n">
-        <v>7044740</v>
+        <v>7044912</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,11 +2314,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,10 +2340,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133804713</v>
+        <v>133804654</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2351,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486386</v>
+        <v>486481</v>
       </c>
       <c r="R19" t="n">
-        <v>7044674</v>
+        <v>7044756</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,7 +2437,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133804715</v>
+        <v>133804712</v>
       </c>
       <c r="B20" t="n">
         <v>79359</v>
@@ -2529,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486526</v>
+        <v>486211</v>
       </c>
       <c r="R20" t="n">
-        <v>7044708</v>
+        <v>7044745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,10 +2534,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133804707</v>
+        <v>133804717</v>
       </c>
       <c r="B21" t="n">
-        <v>91956</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,21 +2545,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486370</v>
+        <v>486308</v>
       </c>
       <c r="R21" t="n">
-        <v>7044652</v>
+        <v>7044783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133804650</v>
+        <v>133804718</v>
       </c>
       <c r="B22" t="n">
-        <v>97421</v>
+        <v>83208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2699,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2723,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486266</v>
+        <v>486359</v>
       </c>
       <c r="R22" t="n">
-        <v>7044804</v>
+        <v>7044653</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,10 +2728,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133804655</v>
+        <v>133804690</v>
       </c>
       <c r="B23" t="n">
-        <v>91960</v>
+        <v>58136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2796,34 +2739,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486471</v>
+        <v>486258</v>
       </c>
       <c r="R23" t="n">
-        <v>7044756</v>
+        <v>7044750</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,10 +2841,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133804673</v>
+        <v>133804649</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,21 +2852,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2917,10 +2876,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486235</v>
+        <v>486379</v>
       </c>
       <c r="R24" t="n">
-        <v>7044839</v>
+        <v>7044657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,11 +2912,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,10 +2938,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133804664</v>
+        <v>133804695</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2995,16 +2949,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3019,10 +2973,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486295</v>
+        <v>486377</v>
       </c>
       <c r="R25" t="n">
-        <v>7044897</v>
+        <v>7044654</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3013,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska födosöksspår i stambasen av en gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3086,10 +3040,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133804710</v>
+        <v>133804703</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>91956</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3097,21 +3051,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3121,10 +3075,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486224</v>
+        <v>486259</v>
       </c>
       <c r="R26" t="n">
-        <v>7044799</v>
+        <v>7044846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3183,10 +3137,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133804685</v>
+        <v>133804698</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>92231</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3194,21 +3148,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3218,10 +3172,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486336</v>
+        <v>486476</v>
       </c>
       <c r="R27" t="n">
-        <v>7044642</v>
+        <v>7044758</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3254,11 +3208,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3285,10 +3234,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804700</v>
+        <v>133804666</v>
       </c>
       <c r="B28" t="n">
-        <v>57153</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3296,16 +3245,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3313,25 +3262,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486493</v>
+        <v>486263</v>
       </c>
       <c r="R28" t="n">
-        <v>7044752</v>
+        <v>7044932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3364,6 +3305,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3390,7 +3336,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804678</v>
+        <v>133804681</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3425,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486227</v>
+        <v>486221</v>
       </c>
       <c r="R29" t="n">
-        <v>7044804</v>
+        <v>7044782</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,7 +3438,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133804688</v>
+        <v>133804679</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3527,10 +3473,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486408</v>
+        <v>486219</v>
       </c>
       <c r="R30" t="n">
-        <v>7044700</v>
+        <v>7044793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3567,7 +3513,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3594,7 +3540,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133804669</v>
+        <v>133804670</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3629,10 +3575,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486251</v>
+        <v>486250</v>
       </c>
       <c r="R31" t="n">
-        <v>7044893</v>
+        <v>7044887</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,7 +3615,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3696,7 +3642,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804683</v>
+        <v>133804676</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3731,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486301</v>
+        <v>486230</v>
       </c>
       <c r="R32" t="n">
-        <v>7044659</v>
+        <v>7044828</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3771,7 +3717,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3798,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133804705</v>
+        <v>133804661</v>
       </c>
       <c r="B33" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3833,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486296</v>
+        <v>486467</v>
       </c>
       <c r="R33" t="n">
-        <v>7044912</v>
+        <v>7044758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3869,6 +3815,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3895,45 +3846,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133804697</v>
+        <v>133804665</v>
       </c>
       <c r="B34" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486485</v>
+        <v>486305</v>
       </c>
       <c r="R34" t="n">
-        <v>7044754</v>
+        <v>7044896</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,6 +3937,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 födosökande/ringhackande hona</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3992,10 +3968,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133804654</v>
+        <v>133804660</v>
       </c>
       <c r="B35" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,21 +3979,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4027,10 +4003,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486481</v>
+        <v>486477</v>
       </c>
       <c r="R35" t="n">
-        <v>7044756</v>
+        <v>7044740</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,6 +4039,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4089,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133804712</v>
+        <v>133804689</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4100,21 +4081,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4124,10 +4105,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486211</v>
+        <v>486443</v>
       </c>
       <c r="R36" t="n">
-        <v>7044745</v>
+        <v>7044686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4160,6 +4141,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4186,7 +4172,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133804668</v>
+        <v>133804673</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4221,10 +4207,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486251</v>
+        <v>486235</v>
       </c>
       <c r="R37" t="n">
-        <v>7044896</v>
+        <v>7044839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,7 +4247,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4288,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133804717</v>
+        <v>133804664</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,21 +4285,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4323,10 +4309,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486308</v>
+        <v>486295</v>
       </c>
       <c r="R38" t="n">
-        <v>7044783</v>
+        <v>7044897</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4359,6 +4345,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4385,7 +4376,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133804659</v>
+        <v>133804685</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4420,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486490</v>
+        <v>486336</v>
       </c>
       <c r="R39" t="n">
-        <v>7044755</v>
+        <v>7044642</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4460,7 +4451,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4487,7 +4478,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133804662</v>
+        <v>133804678</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4522,10 +4513,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486445</v>
+        <v>486227</v>
       </c>
       <c r="R40" t="n">
-        <v>7044781</v>
+        <v>7044804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,7 +4553,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4589,10 +4580,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133804718</v>
+        <v>133804688</v>
       </c>
       <c r="B41" t="n">
-        <v>83208</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4600,21 +4591,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4624,10 +4615,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486359</v>
+        <v>486408</v>
       </c>
       <c r="R41" t="n">
-        <v>7044653</v>
+        <v>7044700</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,6 +4651,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4686,7 +4682,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804663</v>
+        <v>133804683</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4721,10 +4717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486306</v>
+        <v>486301</v>
       </c>
       <c r="R42" t="n">
-        <v>7044842</v>
+        <v>7044659</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4761,7 +4757,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4788,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133804690</v>
+        <v>133804669</v>
       </c>
       <c r="B43" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4799,50 +4795,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486258</v>
+        <v>486251</v>
       </c>
       <c r="R43" t="n">
-        <v>7044750</v>
+        <v>7044893</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,6 +4855,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4901,10 +4886,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133804649</v>
+        <v>133804668</v>
       </c>
       <c r="B44" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,21 +4897,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4936,10 +4921,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486379</v>
+        <v>486251</v>
       </c>
       <c r="R44" t="n">
-        <v>7044657</v>
+        <v>7044896</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,6 +4957,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4998,7 +4988,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133804675</v>
+        <v>133804659</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -5033,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486233</v>
+        <v>486490</v>
       </c>
       <c r="R45" t="n">
-        <v>7044831</v>
+        <v>7044755</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5073,7 +5063,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5100,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133804671</v>
+        <v>133804662</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5135,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486238</v>
+        <v>486445</v>
       </c>
       <c r="R46" t="n">
-        <v>7044831</v>
+        <v>7044781</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5175,7 +5165,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5202,7 +5192,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133804682</v>
+        <v>133804663</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -5237,10 +5227,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486202</v>
+        <v>486306</v>
       </c>
       <c r="R47" t="n">
-        <v>7044742</v>
+        <v>7044842</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5304,7 +5294,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133804677</v>
+        <v>133804682</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486228</v>
+        <v>486202</v>
       </c>
       <c r="R48" t="n">
-        <v>7044815</v>
+        <v>7044742</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,7 +5369,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5406,10 +5396,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133804695</v>
+        <v>133804671</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5417,16 +5407,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5441,10 +5431,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486377</v>
+        <v>486238</v>
       </c>
       <c r="R49" t="n">
-        <v>7044654</v>
+        <v>7044831</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,7 +5471,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska födosöksspår i stambasen av en gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5508,7 +5498,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133804686</v>
+        <v>133804675</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5543,10 +5533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486374</v>
+        <v>486233</v>
       </c>
       <c r="R50" t="n">
-        <v>7044674</v>
+        <v>7044831</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5610,7 +5600,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133804680</v>
+        <v>133804677</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5645,10 +5635,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486219</v>
+        <v>486228</v>
       </c>
       <c r="R51" t="n">
-        <v>7044788</v>
+        <v>7044815</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,7 +5675,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5712,10 +5702,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133804703</v>
+        <v>133804686</v>
       </c>
       <c r="B52" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5723,21 +5713,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5747,10 +5737,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486259</v>
+        <v>486374</v>
       </c>
       <c r="R52" t="n">
-        <v>7044846</v>
+        <v>7044674</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5783,6 +5773,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5809,7 +5804,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133804667</v>
+        <v>133804680</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5844,10 +5839,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486258</v>
+        <v>486219</v>
       </c>
       <c r="R53" t="n">
-        <v>7044915</v>
+        <v>7044788</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5884,7 +5879,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6013,7 +6008,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133804672</v>
+        <v>133804667</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6048,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486238</v>
+        <v>486258</v>
       </c>
       <c r="R55" t="n">
-        <v>7044839</v>
+        <v>7044915</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6115,10 +6110,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133804698</v>
+        <v>133804672</v>
       </c>
       <c r="B56" t="n">
-        <v>92231</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,21 +6121,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6150,10 +6145,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486476</v>
+        <v>486238</v>
       </c>
       <c r="R56" t="n">
-        <v>7044758</v>
+        <v>7044839</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6186,6 +6181,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 18322-2026 artfynd.xlsx
+++ b/artfynd/A 18322-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133804657</v>
+        <v>133804702</v>
       </c>
       <c r="B2" t="n">
-        <v>91960</v>
+        <v>57153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486285</v>
+        <v>486313</v>
       </c>
       <c r="R2" t="n">
-        <v>7044755</v>
+        <v>7044870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +783,7 @@
         <v>133804708</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804702</v>
+        <v>133804657</v>
       </c>
       <c r="B4" t="n">
-        <v>57153</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486313</v>
+        <v>486285</v>
       </c>
       <c r="R4" t="n">
-        <v>7044870</v>
+        <v>7044755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>133804652</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133804651</v>
+        <v>133804658</v>
       </c>
       <c r="B6" t="n">
-        <v>91960</v>
+        <v>92192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486539</v>
+        <v>486571</v>
       </c>
       <c r="R6" t="n">
-        <v>7044715</v>
+        <v>7044726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133804658</v>
+        <v>133804651</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486571</v>
+        <v>486539</v>
       </c>
       <c r="R7" t="n">
-        <v>7044726</v>
+        <v>7044715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>133804653</v>
       </c>
       <c r="B8" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>133804721</v>
       </c>
       <c r="B9" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>133804715</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>133804713</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>133804650</v>
       </c>
       <c r="B12" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>133804707</v>
       </c>
       <c r="B13" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>133804655</v>
       </c>
       <c r="B14" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>133804710</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804697</v>
+        <v>133804705</v>
       </c>
       <c r="B17" t="n">
-        <v>92392</v>
+        <v>91963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486485</v>
+        <v>486296</v>
       </c>
       <c r="R17" t="n">
-        <v>7044754</v>
+        <v>7044912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804705</v>
+        <v>133804697</v>
       </c>
       <c r="B18" t="n">
-        <v>91956</v>
+        <v>92399</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486296</v>
+        <v>486485</v>
       </c>
       <c r="R18" t="n">
-        <v>7044912</v>
+        <v>7044754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>133804654</v>
       </c>
       <c r="B19" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>133804712</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>133804717</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>133804718</v>
       </c>
       <c r="B22" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>133804649</v>
       </c>
       <c r="B24" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>133804703</v>
       </c>
       <c r="B26" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>133804698</v>
       </c>
       <c r="B27" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804666</v>
+        <v>133804681</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486263</v>
+        <v>486221</v>
       </c>
       <c r="R28" t="n">
-        <v>7044932</v>
+        <v>7044782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3336,7 +3336,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804681</v>
+        <v>133804666</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486221</v>
+        <v>486263</v>
       </c>
       <c r="R29" t="n">
-        <v>7044782</v>
+        <v>7044932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804676</v>
+        <v>133804665</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3670,17 +3670,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486230</v>
+        <v>486305</v>
       </c>
       <c r="R32" t="n">
-        <v>7044828</v>
+        <v>7044896</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,7 +3737,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>1 födosökande/ringhackande hona</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3846,7 +3866,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133804665</v>
+        <v>133804676</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3874,37 +3894,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486305</v>
+        <v>486230</v>
       </c>
       <c r="R34" t="n">
-        <v>7044896</v>
+        <v>7044828</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 födosökande/ringhackande hona</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4682,7 +4682,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804683</v>
+        <v>133804669</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486301</v>
+        <v>486251</v>
       </c>
       <c r="R42" t="n">
-        <v>7044659</v>
+        <v>7044893</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4784,7 +4784,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133804669</v>
+        <v>133804683</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486251</v>
+        <v>486301</v>
       </c>
       <c r="R43" t="n">
-        <v>7044893</v>
+        <v>7044659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5294,7 +5294,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133804682</v>
+        <v>133804675</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486202</v>
+        <v>486233</v>
       </c>
       <c r="R48" t="n">
-        <v>7044742</v>
+        <v>7044831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133804675</v>
+        <v>133804682</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486233</v>
+        <v>486202</v>
       </c>
       <c r="R50" t="n">
-        <v>7044831</v>
+        <v>7044742</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133804674</v>
+        <v>133804667</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486239</v>
+        <v>486258</v>
       </c>
       <c r="R54" t="n">
-        <v>7044840</v>
+        <v>7044915</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133804667</v>
+        <v>133804674</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486258</v>
+        <v>486239</v>
       </c>
       <c r="R55" t="n">
-        <v>7044915</v>
+        <v>7044840</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 18322-2026 artfynd.xlsx
+++ b/artfynd/A 18322-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133804702</v>
+        <v>133804650</v>
       </c>
       <c r="B2" t="n">
-        <v>57153</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486313</v>
+        <v>486266</v>
       </c>
       <c r="R2" t="n">
-        <v>7044870</v>
+        <v>7044804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133804708</v>
+        <v>133804698</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486257</v>
+        <v>486476</v>
       </c>
       <c r="R3" t="n">
-        <v>7044707</v>
+        <v>7044758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804657</v>
+        <v>133804703</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486285</v>
+        <v>486259</v>
       </c>
       <c r="R4" t="n">
-        <v>7044755</v>
+        <v>7044846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133804652</v>
+        <v>133804705</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486530</v>
+        <v>486296</v>
       </c>
       <c r="R5" t="n">
-        <v>7044741</v>
+        <v>7044912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133804658</v>
+        <v>133804707</v>
       </c>
       <c r="B6" t="n">
-        <v>92192</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486571</v>
+        <v>486370</v>
       </c>
       <c r="R6" t="n">
-        <v>7044726</v>
+        <v>7044652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1163,7 @@
         <v>133804651</v>
       </c>
       <c r="B7" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133804653</v>
+        <v>133804652</v>
       </c>
       <c r="B8" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486466</v>
+        <v>486530</v>
       </c>
       <c r="R8" t="n">
-        <v>7044734</v>
+        <v>7044741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133804721</v>
+        <v>133804653</v>
       </c>
       <c r="B9" t="n">
-        <v>83215</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486382</v>
+        <v>486466</v>
       </c>
       <c r="R9" t="n">
-        <v>7044675</v>
+        <v>7044734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133804715</v>
+        <v>133804654</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486526</v>
+        <v>486481</v>
       </c>
       <c r="R10" t="n">
-        <v>7044708</v>
+        <v>7044756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133804713</v>
+        <v>133804655</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486386</v>
+        <v>486471</v>
       </c>
       <c r="R11" t="n">
-        <v>7044674</v>
+        <v>7044756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133804650</v>
+        <v>133804657</v>
       </c>
       <c r="B12" t="n">
-        <v>97428</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486266</v>
+        <v>486285</v>
       </c>
       <c r="R12" t="n">
-        <v>7044804</v>
+        <v>7044755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133804707</v>
+        <v>133804697</v>
       </c>
       <c r="B13" t="n">
-        <v>91963</v>
+        <v>92406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486370</v>
+        <v>486485</v>
       </c>
       <c r="R13" t="n">
-        <v>7044652</v>
+        <v>7044754</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133804655</v>
+        <v>133804718</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486471</v>
+        <v>486359</v>
       </c>
       <c r="R14" t="n">
-        <v>7044756</v>
+        <v>7044653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133804710</v>
+        <v>133804721</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>83222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1979,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486224</v>
+        <v>486382</v>
       </c>
       <c r="R15" t="n">
-        <v>7044799</v>
+        <v>7044675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,53 +2033,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133804700</v>
+        <v>133804658</v>
       </c>
       <c r="B16" t="n">
-        <v>57153</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486493</v>
+        <v>486571</v>
       </c>
       <c r="R16" t="n">
-        <v>7044752</v>
+        <v>7044726</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804705</v>
+        <v>133804708</v>
       </c>
       <c r="B17" t="n">
-        <v>91963</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486296</v>
+        <v>486257</v>
       </c>
       <c r="R17" t="n">
-        <v>7044912</v>
+        <v>7044707</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804697</v>
+        <v>133804710</v>
       </c>
       <c r="B18" t="n">
-        <v>92399</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2254,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486485</v>
+        <v>486224</v>
       </c>
       <c r="R18" t="n">
-        <v>7044754</v>
+        <v>7044799</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133804654</v>
+        <v>133804712</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486481</v>
+        <v>486211</v>
       </c>
       <c r="R19" t="n">
-        <v>7044756</v>
+        <v>7044745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,14 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133804712</v>
+        <v>133804713</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2472,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486211</v>
+        <v>486386</v>
       </c>
       <c r="R20" t="n">
-        <v>7044745</v>
+        <v>7044674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,14 +2518,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133804717</v>
+        <v>133804715</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2569,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486308</v>
+        <v>486526</v>
       </c>
       <c r="R21" t="n">
-        <v>7044783</v>
+        <v>7044708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2631,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133804718</v>
+        <v>133804717</v>
       </c>
       <c r="B22" t="n">
-        <v>83215</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486359</v>
+        <v>486308</v>
       </c>
       <c r="R22" t="n">
-        <v>7044653</v>
+        <v>7044783</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2728,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133804690</v>
+        <v>133804649</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>83358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2739,50 +2723,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486258</v>
+        <v>486379</v>
       </c>
       <c r="R23" t="n">
-        <v>7044750</v>
+        <v>7044657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2841,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133804649</v>
+        <v>133804695</v>
       </c>
       <c r="B24" t="n">
-        <v>83351</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2876,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486379</v>
+        <v>486377</v>
       </c>
       <c r="R24" t="n">
-        <v>7044657</v>
+        <v>7044654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2912,6 +2880,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska födosöksspår i stambasen av en gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2938,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133804695</v>
+        <v>133804659</v>
       </c>
       <c r="B25" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2949,16 +2922,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2973,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486377</v>
+        <v>486490</v>
       </c>
       <c r="R25" t="n">
-        <v>7044654</v>
+        <v>7044755</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +2986,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska födosöksspår i stambasen av en gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3040,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133804703</v>
+        <v>133804660</v>
       </c>
       <c r="B26" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3051,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3075,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486259</v>
+        <v>486477</v>
       </c>
       <c r="R26" t="n">
-        <v>7044846</v>
+        <v>7044740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3111,6 +3084,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3137,10 +3115,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133804698</v>
+        <v>133804661</v>
       </c>
       <c r="B27" t="n">
-        <v>92238</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3148,21 +3126,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3172,7 +3150,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486476</v>
+        <v>486467</v>
       </c>
       <c r="R27" t="n">
         <v>7044758</v>
@@ -3208,6 +3186,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3234,7 +3217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804681</v>
+        <v>133804662</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3269,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486221</v>
+        <v>486445</v>
       </c>
       <c r="R28" t="n">
-        <v>7044782</v>
+        <v>7044781</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,7 +3292,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3336,7 +3319,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804666</v>
+        <v>133804663</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3371,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486263</v>
+        <v>486306</v>
       </c>
       <c r="R29" t="n">
-        <v>7044932</v>
+        <v>7044842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3394,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3438,7 +3421,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133804679</v>
+        <v>133804664</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3473,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486219</v>
+        <v>486295</v>
       </c>
       <c r="R30" t="n">
-        <v>7044793</v>
+        <v>7044897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3540,7 +3523,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133804670</v>
+        <v>133804665</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3568,17 +3551,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486250</v>
+        <v>486305</v>
       </c>
       <c r="R31" t="n">
-        <v>7044887</v>
+        <v>7044896</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,7 +3618,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>1 födosökande/ringhackande hona</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3642,7 +3645,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804665</v>
+        <v>133804666</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3670,37 +3673,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486305</v>
+        <v>486263</v>
       </c>
       <c r="R32" t="n">
-        <v>7044896</v>
+        <v>7044932</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3737,7 +3720,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 födosökande/ringhackande hona</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3764,7 +3747,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133804661</v>
+        <v>133804667</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3799,10 +3782,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486467</v>
+        <v>486258</v>
       </c>
       <c r="R33" t="n">
-        <v>7044758</v>
+        <v>7044915</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3866,7 +3849,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133804676</v>
+        <v>133804668</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3901,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486230</v>
+        <v>486251</v>
       </c>
       <c r="R34" t="n">
-        <v>7044828</v>
+        <v>7044896</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,7 +3924,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3968,7 +3951,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133804660</v>
+        <v>133804669</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4003,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486477</v>
+        <v>486251</v>
       </c>
       <c r="R35" t="n">
-        <v>7044740</v>
+        <v>7044893</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,7 +4053,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133804689</v>
+        <v>133804670</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4105,10 +4088,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486443</v>
+        <v>486250</v>
       </c>
       <c r="R36" t="n">
-        <v>7044686</v>
+        <v>7044887</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4145,7 +4128,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4172,7 +4155,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133804673</v>
+        <v>133804671</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4207,10 +4190,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486235</v>
+        <v>486238</v>
       </c>
       <c r="R37" t="n">
-        <v>7044839</v>
+        <v>7044831</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4247,7 +4230,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4274,7 +4257,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133804664</v>
+        <v>133804672</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4309,10 +4292,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486295</v>
+        <v>486238</v>
       </c>
       <c r="R38" t="n">
-        <v>7044897</v>
+        <v>7044839</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4376,7 +4359,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133804685</v>
+        <v>133804673</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4411,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486336</v>
+        <v>486235</v>
       </c>
       <c r="R39" t="n">
-        <v>7044642</v>
+        <v>7044839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4451,7 +4434,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,7 +4461,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133804678</v>
+        <v>133804674</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4513,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486227</v>
+        <v>486239</v>
       </c>
       <c r="R40" t="n">
-        <v>7044804</v>
+        <v>7044840</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4553,7 +4536,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4580,7 +4563,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133804688</v>
+        <v>133804675</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4615,10 +4598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486408</v>
+        <v>486233</v>
       </c>
       <c r="R41" t="n">
-        <v>7044700</v>
+        <v>7044831</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4638,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4682,7 +4665,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804669</v>
+        <v>133804676</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4717,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486251</v>
+        <v>486230</v>
       </c>
       <c r="R42" t="n">
-        <v>7044893</v>
+        <v>7044828</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4757,7 +4740,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4784,7 +4767,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133804683</v>
+        <v>133804677</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -4819,10 +4802,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486301</v>
+        <v>486228</v>
       </c>
       <c r="R43" t="n">
-        <v>7044659</v>
+        <v>7044815</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4859,7 +4842,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,7 +4869,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133804668</v>
+        <v>133804678</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -4921,10 +4904,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486251</v>
+        <v>486227</v>
       </c>
       <c r="R44" t="n">
-        <v>7044896</v>
+        <v>7044804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4988,7 +4971,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133804659</v>
+        <v>133804679</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -5023,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486490</v>
+        <v>486219</v>
       </c>
       <c r="R45" t="n">
-        <v>7044755</v>
+        <v>7044793</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5090,7 +5073,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133804662</v>
+        <v>133804680</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5125,10 +5108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486445</v>
+        <v>486219</v>
       </c>
       <c r="R46" t="n">
-        <v>7044781</v>
+        <v>7044788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5165,7 +5148,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5192,7 +5175,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133804663</v>
+        <v>133804681</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -5227,10 +5210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486306</v>
+        <v>486221</v>
       </c>
       <c r="R47" t="n">
-        <v>7044842</v>
+        <v>7044782</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,7 +5277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133804675</v>
+        <v>133804682</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5329,10 +5312,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486233</v>
+        <v>486202</v>
       </c>
       <c r="R48" t="n">
-        <v>7044831</v>
+        <v>7044742</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5396,7 +5379,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133804671</v>
+        <v>133804683</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5431,10 +5414,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486238</v>
+        <v>486301</v>
       </c>
       <c r="R49" t="n">
-        <v>7044831</v>
+        <v>7044659</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,7 +5454,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5498,7 +5481,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133804682</v>
+        <v>133804685</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5533,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486202</v>
+        <v>486336</v>
       </c>
       <c r="R50" t="n">
-        <v>7044742</v>
+        <v>7044642</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5600,7 +5583,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133804677</v>
+        <v>133804686</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5635,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486228</v>
+        <v>486374</v>
       </c>
       <c r="R51" t="n">
-        <v>7044815</v>
+        <v>7044674</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,7 +5658,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5702,7 +5685,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133804686</v>
+        <v>133804687</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5737,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486374</v>
+        <v>486397</v>
       </c>
       <c r="R52" t="n">
-        <v>7044674</v>
+        <v>7044689</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,7 +5760,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5804,7 +5787,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133804680</v>
+        <v>133804688</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5839,10 +5822,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486219</v>
+        <v>486408</v>
       </c>
       <c r="R53" t="n">
-        <v>7044788</v>
+        <v>7044700</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,7 +5862,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5906,7 +5889,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133804667</v>
+        <v>133804689</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -5941,10 +5924,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486258</v>
+        <v>486443</v>
       </c>
       <c r="R54" t="n">
-        <v>7044915</v>
+        <v>7044686</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5981,7 +5964,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6008,27 +5991,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133804674</v>
+        <v>133804700</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6036,17 +6019,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486239</v>
+        <v>486493</v>
       </c>
       <c r="R55" t="n">
-        <v>7044840</v>
+        <v>7044752</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6079,11 +6070,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6110,27 +6096,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133804672</v>
+        <v>133804702</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>57153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6138,17 +6124,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486238</v>
+        <v>486313</v>
       </c>
       <c r="R56" t="n">
-        <v>7044839</v>
+        <v>7044870</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6181,11 +6175,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6212,10 +6201,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133804687</v>
+        <v>133804690</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,34 +6212,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mässelströmmen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486397</v>
+        <v>486258</v>
       </c>
       <c r="R57" t="n">
-        <v>7044689</v>
+        <v>7044750</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6283,11 +6288,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 18322-2026 artfynd.xlsx
+++ b/artfynd/A 18322-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804653</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804654</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804718</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804721</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804658</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804708</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804710</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804712</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804713</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804715</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804717</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804649</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804695</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804659</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3112,6 +3237,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804660</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804661</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804662</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3418,6 +3558,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804663</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3520,6 +3665,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804664</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3642,6 +3792,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804665</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3744,6 +3899,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804666</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3846,6 +4006,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804667</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3948,6 +4113,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804668</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4050,6 +4220,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804669</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4152,6 +4327,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804670</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4254,6 +4434,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804671</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4356,6 +4541,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804672</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4458,6 +4648,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804673</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4560,6 +4755,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804674</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4662,6 +4862,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804675</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4764,6 +4969,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804676</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4866,6 +5076,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804677</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4968,6 +5183,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804678</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5070,6 +5290,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804679</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5172,6 +5397,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804680</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5274,6 +5504,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804681</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5376,6 +5611,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804682</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5478,6 +5718,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804683</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5580,6 +5825,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804685</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5682,6 +5932,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804686</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5784,6 +6039,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804687</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5886,6 +6146,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804688</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5988,6 +6253,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804689</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6093,6 +6363,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804700</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6198,6 +6473,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804702</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6311,8 +6591,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133804690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>